--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -422,10 +422,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -443,15 +443,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -465,7 +459,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -479,32 +473,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,11 +503,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -543,7 +520,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -557,23 +542,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -582,6 +559,29 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -596,7 +596,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,7 +626,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,13 +638,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +668,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,25 +698,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,7 +752,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,85 +776,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,15 +805,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -833,7 +824,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -855,20 +846,29 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -895,145 +895,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3307,7 +3307,7 @@
         <v>11140</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3370,7 +3370,7 @@
         <v>12140</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3433,7 +3433,7 @@
         <v>3120</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3496,7 +3496,7 @@
         <v>14130</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -3559,7 +3559,7 @@
         <v>5130</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:3">

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
     <sheet name="Learning" sheetId="3" r:id="rId2"/>
     <sheet name="SkillTrigger" sheetId="4" r:id="rId3"/>
-    <sheet name="TextData" sheetId="2" r:id="rId4"/>
+    <sheet name="Heroic" sheetId="5" r:id="rId4"/>
+    <sheet name="TextData" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
   <si>
     <t>Id</t>
   </si>
@@ -197,6 +198,12 @@
   </si>
   <si>
     <t>TriggerType2</t>
+  </si>
+  <si>
+    <t>HeroicId</t>
+  </si>
+  <si>
+    <t>InitLevel</t>
   </si>
   <si>
     <t>Text</t>
@@ -422,10 +429,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -443,9 +450,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -474,7 +480,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -489,22 +518,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -512,7 +525,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -520,29 +533,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -558,17 +549,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -580,8 +571,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -596,7 +603,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,13 +639,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,121 +753,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,31 +765,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -790,17 +797,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -820,37 +821,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -873,16 +869,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -895,145 +902,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5880,6 +5887,777 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:C69"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1050</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1080</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1290</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1320</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>2020</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>2190</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>2310</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2390</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1100</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>1140</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>1210</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>1280</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>2010</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>2120</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>2170</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>2200</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1040</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>1150</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>1240</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>1360</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>2250</v>
+      </c>
+      <c r="C23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>2310</v>
+      </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>4</v>
+      </c>
+      <c r="B25">
+        <v>1030</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>1160</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>1250</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>1400</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>2170</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>2290</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <v>1050</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>5</v>
+      </c>
+      <c r="B32">
+        <v>1180</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>5</v>
+      </c>
+      <c r="B33">
+        <v>1220</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34">
+        <v>1340</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35">
+        <v>2220</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>5</v>
+      </c>
+      <c r="B36">
+        <v>2320</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>6</v>
+      </c>
+      <c r="B37">
+        <v>1010</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38">
+        <v>1110</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>1300</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>6</v>
+      </c>
+      <c r="B40">
+        <v>2050</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>6</v>
+      </c>
+      <c r="B41">
+        <v>2310</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>7</v>
+      </c>
+      <c r="B42">
+        <v>1120</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>1160</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>7</v>
+      </c>
+      <c r="B44">
+        <v>1290</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>1400</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46">
+        <v>2080</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>7</v>
+      </c>
+      <c r="B47">
+        <v>2100</v>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>7</v>
+      </c>
+      <c r="B48">
+        <v>2270</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49">
+        <v>2360</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>8</v>
+      </c>
+      <c r="B50">
+        <v>1040</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>8</v>
+      </c>
+      <c r="B51">
+        <v>1110</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>8</v>
+      </c>
+      <c r="B52">
+        <v>1130</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>8</v>
+      </c>
+      <c r="B53">
+        <v>1270</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54">
+        <v>1370</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>8</v>
+      </c>
+      <c r="B55">
+        <v>2040</v>
+      </c>
+      <c r="C55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>2240</v>
+      </c>
+      <c r="C56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>8</v>
+      </c>
+      <c r="B57">
+        <v>2260</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>9</v>
+      </c>
+      <c r="B58">
+        <v>1110</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>9</v>
+      </c>
+      <c r="B59">
+        <v>1170</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>9</v>
+      </c>
+      <c r="B60">
+        <v>1190</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>9</v>
+      </c>
+      <c r="B61">
+        <v>2120</v>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>9</v>
+      </c>
+      <c r="B62">
+        <v>2230</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>9</v>
+      </c>
+      <c r="B63">
+        <v>2280</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>9</v>
+      </c>
+      <c r="B64">
+        <v>2370</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>10</v>
+      </c>
+      <c r="B65">
+        <v>1050</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>10</v>
+      </c>
+      <c r="B66">
+        <v>1110</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>10</v>
+      </c>
+      <c r="B67">
+        <v>1200</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>10</v>
+      </c>
+      <c r="B68">
+        <v>2030</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>10</v>
+      </c>
+      <c r="B69">
+        <v>2180</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
@@ -5893,22 +6671,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:7">
@@ -5916,22 +6694,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:7">
@@ -5939,22 +6717,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" t="s">
         <v>73</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:7">
@@ -5962,22 +6740,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:7">
@@ -5985,22 +6763,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:7">
@@ -6008,22 +6786,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:7">
@@ -6031,22 +6809,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:7">
@@ -6054,22 +6832,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:7">
@@ -6077,22 +6855,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:7">
@@ -6100,22 +6878,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:7">
@@ -6123,22 +6901,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="39" spans="1:7">
@@ -6146,22 +6924,22 @@
         <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:7">
@@ -6169,22 +6947,22 @@
         <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="39" spans="1:7">
@@ -6192,22 +6970,22 @@
         <v>103</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="39" spans="1:7">
@@ -6215,22 +6993,22 @@
         <v>104</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -429,10 +429,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -450,6 +450,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -464,10 +510,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -479,77 +526,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -571,9 +550,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,9 +564,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -603,7 +603,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -615,115 +753,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,55 +777,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,11 +797,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -821,17 +827,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -854,17 +863,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -879,21 +894,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -902,145 +902,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5909,7 +5909,7 @@
         <v>1050</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5920,7 +5920,7 @@
         <v>1080</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5931,7 +5931,7 @@
         <v>1290</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5942,7 +5942,7 @@
         <v>1320</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5953,7 +5953,7 @@
         <v>2020</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5964,7 +5964,7 @@
         <v>2190</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5972,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>2310</v>
+        <v>2390</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -5983,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>2390</v>
+        <v>2310</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -5997,7 +5997,7 @@
         <v>1100</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6008,7 +6008,7 @@
         <v>1140</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6019,7 +6019,7 @@
         <v>1210</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6030,7 +6030,7 @@
         <v>1280</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6052,7 +6052,7 @@
         <v>2120</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6074,7 +6074,7 @@
         <v>2200</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6085,7 +6085,7 @@
         <v>1040</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6096,7 +6096,7 @@
         <v>1150</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6107,7 +6107,7 @@
         <v>1240</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6118,7 +6118,7 @@
         <v>1360</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6129,7 +6129,7 @@
         <v>2030</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6140,7 +6140,7 @@
         <v>2250</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6162,7 +6162,7 @@
         <v>1030</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6173,7 +6173,7 @@
         <v>1160</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6184,7 +6184,7 @@
         <v>1250</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6195,7 +6195,7 @@
         <v>1400</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6228,7 +6228,7 @@
         <v>1050</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6239,7 +6239,7 @@
         <v>1180</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6250,7 +6250,7 @@
         <v>1220</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6261,7 +6261,7 @@
         <v>1340</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6272,7 +6272,7 @@
         <v>2220</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6294,7 +6294,7 @@
         <v>1010</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6305,7 +6305,7 @@
         <v>1110</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6316,7 +6316,7 @@
         <v>1300</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6327,7 +6327,7 @@
         <v>2050</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6349,7 +6349,7 @@
         <v>1120</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6360,7 +6360,7 @@
         <v>1160</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6371,7 +6371,7 @@
         <v>1290</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6382,7 +6382,7 @@
         <v>1400</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6404,7 +6404,7 @@
         <v>2100</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6437,7 +6437,7 @@
         <v>1040</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6448,7 +6448,7 @@
         <v>1110</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6459,7 +6459,7 @@
         <v>1130</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6470,7 +6470,7 @@
         <v>1270</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6481,7 +6481,7 @@
         <v>1370</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6492,7 +6492,7 @@
         <v>2040</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6514,7 +6514,7 @@
         <v>2260</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6525,7 +6525,7 @@
         <v>1110</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6536,7 +6536,7 @@
         <v>1170</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6547,7 +6547,7 @@
         <v>1190</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6569,7 +6569,7 @@
         <v>2230</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6580,7 +6580,7 @@
         <v>2280</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6602,7 +6602,7 @@
         <v>1050</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -6613,7 +6613,7 @@
         <v>1110</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -6624,7 +6624,7 @@
         <v>1200</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -6635,7 +6635,7 @@
         <v>2030</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -6646,7 +6646,7 @@
         <v>2180</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -430,9 +430,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -450,16 +450,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -474,7 +496,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -483,68 +505,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -564,8 +540,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -579,16 +586,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -603,7 +603,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -621,60 +669,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -687,19 +681,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -711,31 +717,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -753,19 +735,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -777,13 +753,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,17 +797,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -831,15 +825,17 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -860,11 +856,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -886,11 +888,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -902,145 +902,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>10210</v>
+        <v>1040</v>
       </c>
       <c r="C5">
         <v>21</v>
@@ -3385,7 +3385,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>10210</v>
+        <v>2020</v>
       </c>
       <c r="C11">
         <v>21</v>
@@ -3426,7 +3426,7 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>13010</v>
+        <v>3120</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -3437,7 +3437,7 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>3120</v>
+        <v>13120</v>
       </c>
       <c r="C16">
         <v>11</v>
@@ -3448,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>10210</v>
+        <v>3020</v>
       </c>
       <c r="C17">
         <v>21</v>
@@ -3511,7 +3511,7 @@
         <v>4</v>
       </c>
       <c r="B23">
-        <v>10210</v>
+        <v>14140</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -3574,7 +3574,7 @@
         <v>5</v>
       </c>
       <c r="B29">
-        <v>10210</v>
+        <v>15140</v>
       </c>
       <c r="C29">
         <v>21</v>
@@ -3897,7 +3897,7 @@
         <v>101</v>
       </c>
       <c r="B60">
-        <v>10210</v>
+        <v>3130</v>
       </c>
       <c r="C60">
         <v>21</v>
